--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/134.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/134.xlsx
@@ -426,13 +426,13 @@
         <v>-17.28973735286768</v>
       </c>
       <c r="E2">
-        <v>-16.3850490000587</v>
+        <v>-17.92219421722232</v>
       </c>
       <c r="F2">
-        <v>6.234577056240732</v>
+        <v>5.31457399460874</v>
       </c>
       <c r="G2">
-        <v>-6.907451107812126</v>
+        <v>-7.675371872192549</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.01076144044274</v>
       </c>
       <c r="E3">
-        <v>-17.78257230661783</v>
+        <v>-18.46886254248027</v>
       </c>
       <c r="F3">
-        <v>5.940377402932071</v>
+        <v>5.223440326422349</v>
       </c>
       <c r="G3">
-        <v>-5.992979113499247</v>
+        <v>-6.699184687936576</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.69037184592893</v>
       </c>
       <c r="E4">
-        <v>-18.70022227953215</v>
+        <v>-19.16666415927021</v>
       </c>
       <c r="F4">
-        <v>5.885587526176105</v>
+        <v>5.154969133641747</v>
       </c>
       <c r="G4">
-        <v>-4.918071461262207</v>
+        <v>-6.114409923879713</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.37980265490921</v>
       </c>
       <c r="E5">
-        <v>-18.7157187175864</v>
+        <v>-20.89116140307918</v>
       </c>
       <c r="F5">
-        <v>6.429801715528102</v>
+        <v>4.989587238407632</v>
       </c>
       <c r="G5">
-        <v>-5.168673137493957</v>
+        <v>-5.865645600422258</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.07821723811333</v>
       </c>
       <c r="E6">
-        <v>-18.6687222143348</v>
+        <v>-21.01245657937463</v>
       </c>
       <c r="F6">
-        <v>5.667753406996725</v>
+        <v>5.226798527873298</v>
       </c>
       <c r="G6">
-        <v>-3.789797814932114</v>
+        <v>-5.572453755827785</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.80213820925427</v>
       </c>
       <c r="E7">
-        <v>-20.35582331978842</v>
+        <v>-21.75843663113217</v>
       </c>
       <c r="F7">
-        <v>6.056103642572773</v>
+        <v>5.400397827743185</v>
       </c>
       <c r="G7">
-        <v>-4.551739734068613</v>
+        <v>-4.663242218376807</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.55017264314502</v>
       </c>
       <c r="E8">
-        <v>-20.74597852639327</v>
+        <v>-21.9881706460153</v>
       </c>
       <c r="F8">
-        <v>6.108448178755673</v>
+        <v>5.284076820307273</v>
       </c>
       <c r="G8">
-        <v>-2.501062026313548</v>
+        <v>-4.604632320149549</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.30542187364933</v>
       </c>
       <c r="E9">
-        <v>-22.04005337272118</v>
+        <v>-21.76060577018185</v>
       </c>
       <c r="F9">
-        <v>6.002673945092204</v>
+        <v>5.168801212533693</v>
       </c>
       <c r="G9">
-        <v>-2.634195615175339</v>
+        <v>-3.190195117404856</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.05964564691824</v>
       </c>
       <c r="E10">
-        <v>-22.43796132682716</v>
+        <v>-22.98888188917831</v>
       </c>
       <c r="F10">
-        <v>6.117742461015084</v>
+        <v>5.634358603520266</v>
       </c>
       <c r="G10">
-        <v>-1.899165120727575</v>
+        <v>-2.708845106540365</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.77546141429871</v>
       </c>
       <c r="E11">
-        <v>-23.63745446503087</v>
+        <v>-24.68397575125547</v>
       </c>
       <c r="F11">
-        <v>6.552312284197733</v>
+        <v>5.189457382089902</v>
       </c>
       <c r="G11">
-        <v>-1.067595807809124</v>
+        <v>-2.292848575166626</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.43395744062051</v>
       </c>
       <c r="E12">
-        <v>-25.39363291299749</v>
+        <v>-25.01502984358621</v>
       </c>
       <c r="F12">
-        <v>6.163556148594314</v>
+        <v>5.54134122785991</v>
       </c>
       <c r="G12">
-        <v>-1.029825793751579</v>
+        <v>-1.580240405656346</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.9849688389739</v>
       </c>
       <c r="E13">
-        <v>-24.70093035794019</v>
+        <v>-25.81050611624759</v>
       </c>
       <c r="F13">
-        <v>6.629125136724525</v>
+        <v>5.962239675426755</v>
       </c>
       <c r="G13">
-        <v>-0.2126176273824866</v>
+        <v>-1.595379530407433</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.40469638744238</v>
       </c>
       <c r="E14">
-        <v>-25.85566405905208</v>
+        <v>-27.12177104990862</v>
       </c>
       <c r="F14">
-        <v>6.969875724600907</v>
+        <v>6.1552376831354</v>
       </c>
       <c r="G14">
-        <v>-0.04052553861455251</v>
+        <v>-0.4444882369530406</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.66302223835195</v>
       </c>
       <c r="E15">
-        <v>-27.18654181364033</v>
+        <v>-27.62266555989704</v>
       </c>
       <c r="F15">
-        <v>7.057071334154389</v>
+        <v>6.314524451019718</v>
       </c>
       <c r="G15">
-        <v>0.6553908602867222</v>
+        <v>-0.6222744640485212</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.75497400908416</v>
       </c>
       <c r="E16">
-        <v>-28.23012864870796</v>
+        <v>-28.48611422741356</v>
       </c>
       <c r="F16">
-        <v>7.381312559692977</v>
+        <v>6.925399022009796</v>
       </c>
       <c r="G16">
-        <v>1.242972966960887</v>
+        <v>-0.1752051522431829</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.70645024372371</v>
       </c>
       <c r="E17">
-        <v>-29.00289462422088</v>
+        <v>-28.90475353552665</v>
       </c>
       <c r="F17">
-        <v>7.782755970437673</v>
+        <v>7.441612736412364</v>
       </c>
       <c r="G17">
-        <v>2.045588248592872</v>
+        <v>0.4023791069023825</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.557157379973351</v>
       </c>
       <c r="E18">
-        <v>-29.90189181269761</v>
+        <v>-30.65210598765233</v>
       </c>
       <c r="F18">
-        <v>7.685406233260675</v>
+        <v>7.322054469166312</v>
       </c>
       <c r="G18">
-        <v>2.027343832125948</v>
+        <v>0.2542984049307823</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.383076171975546</v>
       </c>
       <c r="E19">
-        <v>-29.92710409173531</v>
+        <v>-30.97855009344326</v>
       </c>
       <c r="F19">
-        <v>8.243517114162037</v>
+        <v>7.542922069774744</v>
       </c>
       <c r="G19">
-        <v>1.7763713747938</v>
+        <v>0.8544970006551093</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.2470655565538</v>
       </c>
       <c r="E20">
-        <v>-31.63972994093317</v>
+        <v>-31.24833846092423</v>
       </c>
       <c r="F20">
-        <v>8.466193869178182</v>
+        <v>8.044317948076033</v>
       </c>
       <c r="G20">
-        <v>2.019454802105865</v>
+        <v>1.288271161574734</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.229546852323247</v>
       </c>
       <c r="E21">
-        <v>-31.26357677596004</v>
+        <v>-31.99816771558829</v>
       </c>
       <c r="F21">
-        <v>8.436084370821227</v>
+        <v>8.197352198804021</v>
       </c>
       <c r="G21">
-        <v>3.311977854821357</v>
+        <v>1.397429779641123</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.378887525725982</v>
       </c>
       <c r="E22">
-        <v>-32.08073085369614</v>
+        <v>-32.4557790710114</v>
       </c>
       <c r="F22">
-        <v>8.076763442508884</v>
+        <v>8.308762644276136</v>
       </c>
       <c r="G22">
-        <v>2.825003227085645</v>
+        <v>1.428625050257676</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.73260164686894</v>
       </c>
       <c r="E23">
-        <v>-32.57883355945883</v>
+        <v>-31.47695394272746</v>
       </c>
       <c r="F23">
-        <v>8.721833019886528</v>
+        <v>8.321902208019344</v>
       </c>
       <c r="G23">
-        <v>3.213197797020584</v>
+        <v>1.737601575983395</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.303931599500068</v>
       </c>
       <c r="E24">
-        <v>-32.82096653617496</v>
+        <v>-32.04141917083555</v>
       </c>
       <c r="F24">
-        <v>8.572986994747096</v>
+        <v>8.200049363067535</v>
       </c>
       <c r="G24">
-        <v>2.766217869944806</v>
+        <v>2.223596282239483</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.076751194161841</v>
       </c>
       <c r="E25">
-        <v>-31.82209611769606</v>
+        <v>-32.40945731038694</v>
       </c>
       <c r="F25">
-        <v>8.704077792974923</v>
+        <v>8.17510059363002</v>
       </c>
       <c r="G25">
-        <v>3.821778694050345</v>
+        <v>1.44087075820744</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.030901183899231</v>
       </c>
       <c r="E26">
-        <v>-31.24335261104178</v>
+        <v>-31.75147909402045</v>
       </c>
       <c r="F26">
-        <v>8.569567494108339</v>
+        <v>7.577077314526973</v>
       </c>
       <c r="G26">
-        <v>2.909137431420683</v>
+        <v>1.668414484758166</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.118348920064801</v>
       </c>
       <c r="E27">
-        <v>-31.61454709697652</v>
+        <v>-32.14746018243617</v>
       </c>
       <c r="F27">
-        <v>8.471806886699552</v>
+        <v>8.014375779934443</v>
       </c>
       <c r="G27">
-        <v>2.352224218622326</v>
+        <v>0.7726503832877077</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.30532384041642</v>
       </c>
       <c r="E28">
-        <v>-31.9634569623195</v>
+        <v>-32.70812149237782</v>
       </c>
       <c r="F28">
-        <v>8.590959253918234</v>
+        <v>7.940283285958444</v>
       </c>
       <c r="G28">
-        <v>1.531801512534601</v>
+        <v>1.304171711799854</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.544950787276162</v>
       </c>
       <c r="E29">
-        <v>-30.59497928804556</v>
+        <v>-32.32507825420202</v>
       </c>
       <c r="F29">
-        <v>8.477446411977812</v>
+        <v>7.756945698901246</v>
       </c>
       <c r="G29">
-        <v>1.243294089878196</v>
+        <v>0.9892295830123681</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.808417476997379</v>
       </c>
       <c r="E30">
-        <v>-29.89055477801941</v>
+        <v>-31.21639686951113</v>
       </c>
       <c r="F30">
-        <v>8.277319474400674</v>
+        <v>7.995881649299541</v>
       </c>
       <c r="G30">
-        <v>1.623503623972413</v>
+        <v>0.8102648017049069</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.07249702551296</v>
       </c>
       <c r="E31">
-        <v>-30.22788307108777</v>
+        <v>-31.24262352672655</v>
       </c>
       <c r="F31">
-        <v>8.601323786862061</v>
+        <v>8.037586634560885</v>
       </c>
       <c r="G31">
-        <v>1.064746437308683</v>
+        <v>0.1090813248506517</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.318768943323765</v>
       </c>
       <c r="E32">
-        <v>-29.79686744351172</v>
+        <v>-31.16333221108924</v>
       </c>
       <c r="F32">
-        <v>8.34494904590003</v>
+        <v>7.328050192427774</v>
       </c>
       <c r="G32">
-        <v>1.107657728588716</v>
+        <v>0.6596051847582145</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.547418358637142</v>
       </c>
       <c r="E33">
-        <v>-29.84808448453847</v>
+        <v>-30.6823765721566</v>
       </c>
       <c r="F33">
-        <v>8.011753168737179</v>
+        <v>7.932137120919314</v>
       </c>
       <c r="G33">
-        <v>0.1616560985598174</v>
+        <v>-0.4042949035607491</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.752536725381398</v>
       </c>
       <c r="E34">
-        <v>-29.3104368795038</v>
+        <v>-30.52158178132924</v>
       </c>
       <c r="F34">
-        <v>8.239120139987977</v>
+        <v>7.415035396660945</v>
       </c>
       <c r="G34">
-        <v>0.7732131760293838</v>
+        <v>-0.2058276984814414</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.943771794560325</v>
       </c>
       <c r="E35">
-        <v>-29.12855072098572</v>
+        <v>-28.99419542565215</v>
       </c>
       <c r="F35">
-        <v>8.481694280019367</v>
+        <v>7.785754660435807</v>
       </c>
       <c r="G35">
-        <v>0.1419749053288502</v>
+        <v>-0.2758689104558019</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.121704114265437</v>
       </c>
       <c r="E36">
-        <v>-28.12715567824755</v>
+        <v>-29.68790330193915</v>
       </c>
       <c r="F36">
-        <v>8.490334152030567</v>
+        <v>7.78666089437447</v>
       </c>
       <c r="G36">
-        <v>-0.6675594164802117</v>
+        <v>-0.3719608052786874</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.293438992928663</v>
       </c>
       <c r="E37">
-        <v>-28.21466390997177</v>
+        <v>-29.05789294104404</v>
       </c>
       <c r="F37">
-        <v>8.29165188720391</v>
+        <v>7.910549866402358</v>
       </c>
       <c r="G37">
-        <v>-0.2437433765427143</v>
+        <v>-0.5720170722168453</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.461398362106145</v>
       </c>
       <c r="E38">
-        <v>-26.98797275687799</v>
+        <v>-27.08425717122908</v>
       </c>
       <c r="F38">
-        <v>8.541550451810854</v>
+        <v>7.892990134197815</v>
       </c>
       <c r="G38">
-        <v>-0.4597763362533949</v>
+        <v>-1.095881108896657</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.62291255313515</v>
       </c>
       <c r="E39">
-        <v>-26.88690627397481</v>
+        <v>-26.30017001069699</v>
       </c>
       <c r="F39">
-        <v>8.710235876247335</v>
+        <v>7.957650836925539</v>
       </c>
       <c r="G39">
-        <v>-0.6288756918538279</v>
+        <v>-1.357427448681238</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.781500341809195</v>
       </c>
       <c r="E40">
-        <v>-25.51900371589985</v>
+        <v>-27.49152095263491</v>
       </c>
       <c r="F40">
-        <v>8.312906138024941</v>
+        <v>7.645657851804744</v>
       </c>
       <c r="G40">
-        <v>-0.9000490980666094</v>
+        <v>-1.158761610869574</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.928542648707208</v>
       </c>
       <c r="E41">
-        <v>-25.4249880670266</v>
+        <v>-26.80593715871766</v>
       </c>
       <c r="F41">
-        <v>8.911858845353928</v>
+        <v>7.842519365080046</v>
       </c>
       <c r="G41">
-        <v>-1.211134441300844</v>
+        <v>-0.5060842472567203</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.067145786675814</v>
       </c>
       <c r="E42">
-        <v>-24.83930240971856</v>
+        <v>-26.07656302114624</v>
       </c>
       <c r="F42">
-        <v>8.924448373141676</v>
+        <v>7.458730120423813</v>
       </c>
       <c r="G42">
-        <v>-0.4744354319012877</v>
+        <v>-0.8072379538731416</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.187566265941584</v>
       </c>
       <c r="E43">
-        <v>-23.92211434115302</v>
+        <v>-25.66516474297141</v>
       </c>
       <c r="F43">
-        <v>8.841966174110123</v>
+        <v>7.967713844134747</v>
       </c>
       <c r="G43">
-        <v>-1.523865125668097</v>
+        <v>-1.147538861491445</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.291033055484337</v>
       </c>
       <c r="E44">
-        <v>-24.39563422576508</v>
+        <v>-25.39749117285203</v>
       </c>
       <c r="F44">
-        <v>8.410964957698734</v>
+        <v>7.948868485721058</v>
       </c>
       <c r="G44">
-        <v>-1.209141492886203</v>
+        <v>-1.166084537602442</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.371606531007554</v>
       </c>
       <c r="E45">
-        <v>-23.35599622003213</v>
+        <v>-23.72823678346263</v>
       </c>
       <c r="F45">
-        <v>8.639374015142254</v>
+        <v>7.944063954784821</v>
       </c>
       <c r="G45">
-        <v>-0.7897516523347112</v>
+        <v>-2.172086494985092</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.427255478345826</v>
       </c>
       <c r="E46">
-        <v>-22.44296076213163</v>
+        <v>-24.76115000529419</v>
       </c>
       <c r="F46">
-        <v>8.651047368582503</v>
+        <v>7.965508730108494</v>
       </c>
       <c r="G46">
-        <v>-1.166167301240924</v>
+        <v>-2.118465588885516</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.460238909081218</v>
       </c>
       <c r="E47">
-        <v>-21.50014605915668</v>
+        <v>-23.43110548992335</v>
       </c>
       <c r="F47">
-        <v>8.686870945283971</v>
+        <v>7.954640549783766</v>
       </c>
       <c r="G47">
-        <v>-1.686621476015286</v>
+        <v>-1.949660871838079</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.466435816922996</v>
       </c>
       <c r="E48">
-        <v>-20.91848168676745</v>
+        <v>-23.28075562439469</v>
       </c>
       <c r="F48">
-        <v>8.606141571676742</v>
+        <v>8.170418661069398</v>
       </c>
       <c r="G48">
-        <v>-1.851632307874719</v>
+        <v>-1.73198257099438</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.457448326016913</v>
       </c>
       <c r="E49">
-        <v>-22.5239479912848</v>
+        <v>-22.23302070713603</v>
       </c>
       <c r="F49">
-        <v>8.905039724894083</v>
+        <v>8.171503822367065</v>
       </c>
       <c r="G49">
-        <v>-1.397372491158084</v>
+        <v>-2.568696471680858</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.433245022515773</v>
       </c>
       <c r="E50">
-        <v>-20.91860848403967</v>
+        <v>-22.33972966865277</v>
       </c>
       <c r="F50">
-        <v>8.644203397100574</v>
+        <v>8.330719350654741</v>
       </c>
       <c r="G50">
-        <v>-1.558265004366664</v>
+        <v>-2.370000838959341</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.410377790466025</v>
       </c>
       <c r="E51">
-        <v>-21.64609877642389</v>
+        <v>-22.29931756660832</v>
       </c>
       <c r="F51">
-        <v>8.369026372829801</v>
+        <v>8.249082086374043</v>
       </c>
       <c r="G51">
-        <v>-2.461782403490095</v>
+        <v>-2.59035406059877</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.393964694990076</v>
       </c>
       <c r="E52">
-        <v>-21.76684600736442</v>
+        <v>-21.37183174814934</v>
       </c>
       <c r="F52">
-        <v>8.913820419363757</v>
+        <v>8.255359454552458</v>
       </c>
       <c r="G52">
-        <v>-2.059779548110856</v>
+        <v>-2.315734376479608</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.398108099494156</v>
       </c>
       <c r="E53">
-        <v>-20.75537510995918</v>
+        <v>-21.31397596422734</v>
       </c>
       <c r="F53">
-        <v>8.860816502728229</v>
+        <v>8.349370871096175</v>
       </c>
       <c r="G53">
-        <v>-1.867622242829399</v>
+        <v>-3.493113344793709</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.432196455367424</v>
       </c>
       <c r="E54">
-        <v>-19.76848476946758</v>
+        <v>-21.28991618182459</v>
       </c>
       <c r="F54">
-        <v>8.287150538737098</v>
+        <v>7.823442063793574</v>
       </c>
       <c r="G54">
-        <v>-2.253588815616409</v>
+        <v>-3.492053970221142</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.496723759992851</v>
       </c>
       <c r="E55">
-        <v>-20.0365885446177</v>
+        <v>-20.9328550632678</v>
       </c>
       <c r="F55">
-        <v>8.509686471294769</v>
+        <v>7.696511326662606</v>
       </c>
       <c r="G55">
-        <v>-2.978614841444495</v>
+        <v>-3.493040512791845</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.602248673705442</v>
       </c>
       <c r="E56">
-        <v>-19.36329955763128</v>
+        <v>-20.16843506535102</v>
       </c>
       <c r="F56">
-        <v>8.400590484346074</v>
+        <v>8.180943897289367</v>
       </c>
       <c r="G56">
-        <v>-2.879348133449449</v>
+        <v>-3.357424014775601</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.740738174986723</v>
       </c>
       <c r="E57">
-        <v>-19.30827859843808</v>
+        <v>-20.2494222945042</v>
       </c>
       <c r="F57">
-        <v>8.529066955050666</v>
+        <v>7.963499110789303</v>
       </c>
       <c r="G57">
-        <v>-3.178373159284119</v>
+        <v>-3.939815186044188</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.919317444296095</v>
       </c>
       <c r="E58">
-        <v>-20.30284470237268</v>
+        <v>-19.80598053425109</v>
       </c>
       <c r="F58">
-        <v>8.61277182436875</v>
+        <v>7.869954893460766</v>
       </c>
       <c r="G58">
-        <v>-2.860941500251101</v>
+        <v>-3.325113090312314</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.126534383143492</v>
       </c>
       <c r="E59">
-        <v>-18.75886148945747</v>
+        <v>-18.87609462456804</v>
       </c>
       <c r="F59">
-        <v>8.103327528381859</v>
+        <v>8.027386118362813</v>
       </c>
       <c r="G59">
-        <v>-3.980756702728355</v>
+        <v>-3.442289849674818</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.362917523354504</v>
       </c>
       <c r="E60">
-        <v>-18.85514590380856</v>
+        <v>-19.56415096529348</v>
       </c>
       <c r="F60">
-        <v>8.507436625428765</v>
+        <v>7.745239210764884</v>
       </c>
       <c r="G60">
-        <v>-4.02374744710133</v>
+        <v>-4.250923703097198</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.620107850924862</v>
       </c>
       <c r="E61">
-        <v>-18.45608318883063</v>
+        <v>-18.31019387019952</v>
       </c>
       <c r="F61">
-        <v>8.121753732889731</v>
+        <v>7.935265036232285</v>
       </c>
       <c r="G61">
-        <v>-3.880579594710009</v>
+        <v>-5.240876135705461</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.888939194179823</v>
       </c>
       <c r="E62">
-        <v>-17.92198137894396</v>
+        <v>-18.90792979684197</v>
       </c>
       <c r="F62">
-        <v>8.166606514281714</v>
+        <v>7.904221139444971</v>
       </c>
       <c r="G62">
-        <v>-4.266400503493291</v>
+        <v>-4.625353024679848</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.166906286176475</v>
       </c>
       <c r="E63">
-        <v>-17.6588679821503</v>
+        <v>-17.56367945850907</v>
       </c>
       <c r="F63">
-        <v>8.317902850198626</v>
+        <v>7.859000562926146</v>
       </c>
       <c r="G63">
-        <v>-4.436731382034333</v>
+        <v>-4.821787554798043</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.43684878164515</v>
       </c>
       <c r="E64">
-        <v>-17.9167509914651</v>
+        <v>-17.91659249487483</v>
       </c>
       <c r="F64">
-        <v>7.772712844046132</v>
+        <v>7.505811210129326</v>
       </c>
       <c r="G64">
-        <v>-4.439065316639518</v>
+        <v>-5.615917908212876</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.697623528541246</v>
       </c>
       <c r="E65">
-        <v>-18.20006591080698</v>
+        <v>-19.39175648829548</v>
       </c>
       <c r="F65">
-        <v>8.20030781369721</v>
+        <v>7.666613890360765</v>
       </c>
       <c r="G65">
-        <v>-4.729774252079539</v>
+        <v>-4.874279564868726</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.930324082033239</v>
       </c>
       <c r="E66">
-        <v>-16.68603855345252</v>
+        <v>-18.25699788603141</v>
       </c>
       <c r="F66">
-        <v>7.600175511186634</v>
+        <v>7.440482843274945</v>
       </c>
       <c r="G66">
-        <v>-5.394746981825246</v>
+        <v>-5.578363079615384</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.13283017459378</v>
       </c>
       <c r="E67">
-        <v>-16.69572948782893</v>
+        <v>-18.20681786555242</v>
       </c>
       <c r="F67">
-        <v>7.91185205995956</v>
+        <v>7.10620843175365</v>
       </c>
       <c r="G67">
-        <v>-4.696718454869917</v>
+        <v>-4.947356547102599</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.29160442333971</v>
       </c>
       <c r="E68">
-        <v>-17.30036228038506</v>
+        <v>-17.63983933437007</v>
       </c>
       <c r="F68">
-        <v>7.476644393876756</v>
+        <v>7.389145601853849</v>
       </c>
       <c r="G68">
-        <v>-4.7274105225645</v>
+        <v>-5.087160885226021</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.40130141451245</v>
       </c>
       <c r="E69">
-        <v>-17.31137552917171</v>
+        <v>-16.14672899845703</v>
       </c>
       <c r="F69">
-        <v>7.528783494943761</v>
+        <v>7.398782828218018</v>
       </c>
       <c r="G69">
-        <v>-4.742715174592551</v>
+        <v>-5.790833892325808</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.45734101570323</v>
       </c>
       <c r="E70">
-        <v>-17.00860628549288</v>
+        <v>-18.44846629554972</v>
       </c>
       <c r="F70">
-        <v>7.200012756446666</v>
+        <v>7.162549012287656</v>
       </c>
       <c r="G70">
-        <v>-5.03942612909527</v>
+        <v>-5.449569615955578</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.44917016229988</v>
       </c>
       <c r="E71">
-        <v>-16.95957649741183</v>
+        <v>-18.33808474161276</v>
       </c>
       <c r="F71">
-        <v>7.262541241479584</v>
+        <v>6.628831894663934</v>
       </c>
       <c r="G71">
-        <v>-4.805522844563604</v>
+        <v>-4.827491624762208</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.38262185264442</v>
       </c>
       <c r="E72">
-        <v>-16.80857906010008</v>
+        <v>-17.41360582989487</v>
       </c>
       <c r="F72">
-        <v>7.102724318457475</v>
+        <v>6.461407245414515</v>
       </c>
       <c r="G72">
-        <v>-4.06344750920827</v>
+        <v>-5.184788873179128</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.25154421557808</v>
       </c>
       <c r="E73">
-        <v>-16.45461994623854</v>
+        <v>-17.67196885745449</v>
       </c>
       <c r="F73">
-        <v>7.441907635207761</v>
+        <v>7.006855702196683</v>
       </c>
       <c r="G73">
-        <v>-4.837698036659781</v>
+        <v>-4.986248836097957</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.06905925180265</v>
       </c>
       <c r="E74">
-        <v>-16.72285504713487</v>
+        <v>-17.97636382330208</v>
       </c>
       <c r="F74">
-        <v>7.430655092408132</v>
+        <v>6.518499983550262</v>
       </c>
       <c r="G74">
-        <v>-4.1862323327143</v>
+        <v>-4.955454141491656</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.832555439088575</v>
       </c>
       <c r="E75">
-        <v>-16.32259228654491</v>
+        <v>-17.51725354298243</v>
       </c>
       <c r="F75">
-        <v>7.205617490294007</v>
+        <v>6.67565950394419</v>
       </c>
       <c r="G75">
-        <v>-3.680122751761599</v>
+        <v>-4.882840635633282</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.553887410484936</v>
       </c>
       <c r="E76">
-        <v>-17.15671908486176</v>
+        <v>-18.26686090242012</v>
       </c>
       <c r="F76">
-        <v>6.907958574711255</v>
+        <v>6.433105244730466</v>
       </c>
       <c r="G76">
-        <v>-4.412541225778878</v>
+        <v>-4.232871298271553</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.236942857428756</v>
       </c>
       <c r="E77">
-        <v>-17.18919730044477</v>
+        <v>-17.74216926152139</v>
       </c>
       <c r="F77">
-        <v>6.701290848121612</v>
+        <v>6.345659468221339</v>
       </c>
       <c r="G77">
-        <v>-3.263020498177744</v>
+        <v>-4.368113704641859</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.887786130752849</v>
       </c>
       <c r="E78">
-        <v>-16.9547129163276</v>
+        <v>-18.09314411101188</v>
       </c>
       <c r="F78">
-        <v>6.738181362037886</v>
+        <v>6.055666264584095</v>
       </c>
       <c r="G78">
-        <v>-3.522938049557003</v>
+        <v>-4.036781064889441</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.518964211814682</v>
       </c>
       <c r="E79">
-        <v>-18.71726292722301</v>
+        <v>-19.19411576870471</v>
       </c>
       <c r="F79">
-        <v>6.804412649361317</v>
+        <v>6.354569388005851</v>
       </c>
       <c r="G79">
-        <v>-3.657568005002545</v>
+        <v>-3.487409274829545</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.132856311454161</v>
       </c>
       <c r="E80">
-        <v>-17.02250417222242</v>
+        <v>-19.93107510023898</v>
       </c>
       <c r="F80">
-        <v>6.399276376734941</v>
+        <v>6.29886333690239</v>
       </c>
       <c r="G80">
-        <v>-2.750303068328658</v>
+        <v>-3.835655491742099</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.745497778603422</v>
       </c>
       <c r="E81">
-        <v>-19.092741349569</v>
+        <v>-19.72494349188383</v>
       </c>
       <c r="F81">
-        <v>6.561734135037174</v>
+        <v>5.945170336724669</v>
       </c>
       <c r="G81">
-        <v>-2.04622286412754</v>
+        <v>-2.895705538958988</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.356690490007472</v>
       </c>
       <c r="E82">
-        <v>-18.71085966497617</v>
+        <v>-19.65217997152858</v>
       </c>
       <c r="F82">
-        <v>6.406430157625517</v>
+        <v>5.637491489037654</v>
       </c>
       <c r="G82">
-        <v>-2.077176464919726</v>
+        <v>-3.050132556729371</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.980093340106399</v>
       </c>
       <c r="E83">
-        <v>-19.63862624882363</v>
+        <v>-20.26772185796919</v>
       </c>
       <c r="F83">
-        <v>6.274068643801796</v>
+        <v>5.458486263497098</v>
       </c>
       <c r="G83">
-        <v>-1.936143914401234</v>
+        <v>-2.499853677191714</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.614505450600558</v>
       </c>
       <c r="E84">
-        <v>-20.16392017676537</v>
+        <v>-21.68352208562328</v>
       </c>
       <c r="F84">
-        <v>6.247920398365026</v>
+        <v>5.882494402294053</v>
       </c>
       <c r="G84">
-        <v>-1.907395136938203</v>
+        <v>-2.819682171195164</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.26427123822759</v>
       </c>
       <c r="E85">
-        <v>-20.89746503889786</v>
+        <v>-21.89254738886933</v>
       </c>
       <c r="F85">
-        <v>5.929633477717761</v>
+        <v>5.699769807114926</v>
       </c>
       <c r="G85">
-        <v>-1.934604510725473</v>
+        <v>-2.163717435861814</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.929219665297519</v>
       </c>
       <c r="E86">
-        <v>-21.06439817624261</v>
+        <v>-23.40799668706221</v>
       </c>
       <c r="F86">
-        <v>6.093206218544163</v>
+        <v>5.424087478728445</v>
       </c>
       <c r="G86">
-        <v>-1.034311582957292</v>
+        <v>-1.518518594622174</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.604170410038782</v>
       </c>
       <c r="E87">
-        <v>-23.43576076120324</v>
+        <v>-23.45000281195736</v>
       </c>
       <c r="F87">
-        <v>5.569744289367099</v>
+        <v>5.458973343529943</v>
       </c>
       <c r="G87">
-        <v>-0.3391731622577456</v>
+        <v>-1.547866580827813</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.292401453653834</v>
       </c>
       <c r="E88">
-        <v>-23.85442724016038</v>
+        <v>-25.33911461441915</v>
       </c>
       <c r="F88">
-        <v>5.924918410461026</v>
+        <v>5.178175018063772</v>
       </c>
       <c r="G88">
-        <v>-0.0535558458571239</v>
+        <v>-1.920458549636167</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.986982778392162</v>
       </c>
       <c r="E89">
-        <v>-26.18139719442381</v>
+        <v>-26.38941264796615</v>
       </c>
       <c r="F89">
-        <v>5.846750348863254</v>
+        <v>4.832411150665648</v>
       </c>
       <c r="G89">
-        <v>-0.8690756340011881</v>
+        <v>-1.390099222608305</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.693454762650581</v>
       </c>
       <c r="E90">
-        <v>-26.36256332557467</v>
+        <v>-28.45937358839826</v>
       </c>
       <c r="F90">
-        <v>5.117384447841928</v>
+        <v>4.896296501504351</v>
       </c>
       <c r="G90">
-        <v>-0.4013783129406512</v>
+        <v>-0.8444849017354817</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.405806528617089</v>
       </c>
       <c r="E91">
-        <v>-27.91755978727653</v>
+        <v>-29.71695119846136</v>
       </c>
       <c r="F91">
-        <v>4.928672413075367</v>
+        <v>4.447959212087174</v>
       </c>
       <c r="G91">
-        <v>-0.1014561292648387</v>
+        <v>-1.369206369709965</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.1291097434969</v>
       </c>
       <c r="E92">
-        <v>-29.11665894824158</v>
+        <v>-31.45817888949166</v>
       </c>
       <c r="F92">
-        <v>4.91843213524196</v>
+        <v>4.13101590336725</v>
       </c>
       <c r="G92">
-        <v>0.02425852704344535</v>
+        <v>-1.200027561016589</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.863916791989278</v>
       </c>
       <c r="E93">
-        <v>-32.09293735538382</v>
+        <v>-32.90304965603799</v>
       </c>
       <c r="F93">
-        <v>4.547497495942369</v>
+        <v>3.793628487146234</v>
       </c>
       <c r="G93">
-        <v>0.1528632896075131</v>
+        <v>-1.028544612627881</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.612302687935877</v>
       </c>
       <c r="E94">
-        <v>-33.79067811051846</v>
+        <v>-33.83928675051679</v>
       </c>
       <c r="F94">
-        <v>4.099902423718101</v>
+        <v>3.569684330003805</v>
       </c>
       <c r="G94">
-        <v>-0.5691071026878258</v>
+        <v>-0.3436655725545366</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.380383470910599</v>
       </c>
       <c r="E95">
-        <v>-35.47774072394301</v>
+        <v>-36.46067770662592</v>
       </c>
       <c r="F95">
-        <v>3.535494293820658</v>
+        <v>3.216566216803626</v>
       </c>
       <c r="G95">
-        <v>0.4360738394010847</v>
+        <v>-0.8788417433420381</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.170416426949222</v>
       </c>
       <c r="E96">
-        <v>-37.43548834270206</v>
+        <v>-39.18070561933312</v>
       </c>
       <c r="F96">
-        <v>3.192054825354788</v>
+        <v>2.665889104974987</v>
       </c>
       <c r="G96">
-        <v>0.5557301973725024</v>
+        <v>-1.203953868026165</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.987447894444987</v>
       </c>
       <c r="E97">
-        <v>-39.74785623252777</v>
+        <v>-40.94776372610318</v>
       </c>
       <c r="F97">
-        <v>2.684838837681429</v>
+        <v>2.368472072673853</v>
       </c>
       <c r="G97">
-        <v>-0.5363327018490411</v>
+        <v>-1.070965943168102</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.837560044800972</v>
       </c>
       <c r="E98">
-        <v>-42.27695915259758</v>
+        <v>-43.2857107013612</v>
       </c>
       <c r="F98">
-        <v>2.11528323274299</v>
+        <v>2.038511798586337</v>
       </c>
       <c r="G98">
-        <v>0.005815477844165562</v>
+        <v>-1.555355034837644</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.720900802930259</v>
       </c>
       <c r="E99">
-        <v>-44.60704469697829</v>
+        <v>-45.24319566862781</v>
       </c>
       <c r="F99">
-        <v>1.71818875086299</v>
+        <v>1.459424998311286</v>
       </c>
       <c r="G99">
-        <v>-0.8177257621415528</v>
+        <v>-1.006284504421822</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.656059237122931</v>
       </c>
       <c r="E100">
-        <v>-46.68211375609106</v>
+        <v>-47.67524206952822</v>
       </c>
       <c r="F100">
-        <v>1.410972132186738</v>
+        <v>0.8141731801050284</v>
       </c>
       <c r="G100">
-        <v>-0.9597746501406008</v>
+        <v>-1.616851728775146</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.627965157414058</v>
       </c>
       <c r="E101">
-        <v>-48.45081456680739</v>
+        <v>-50.10772093969637</v>
       </c>
       <c r="F101">
-        <v>0.5043654281928188</v>
+        <v>0.5162856351191037</v>
       </c>
       <c r="G101">
-        <v>-0.5430266249294474</v>
+        <v>-1.446580440053811</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.683580008129994</v>
       </c>
       <c r="E102">
-        <v>-51.41882284829312</v>
+        <v>-52.74693257314418</v>
       </c>
       <c r="F102">
-        <v>0.3009531854961778</v>
+        <v>0.3146825468301768</v>
       </c>
       <c r="G102">
-        <v>-1.681708626435008</v>
+        <v>-1.625522047542497</v>
       </c>
     </row>
   </sheetData>
